--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.53919082563302</v>
+        <v>3.825118509165366</v>
       </c>
       <c r="D2" t="n">
-        <v>24.13238993716986</v>
+        <v>3.921513364790103</v>
       </c>
       <c r="E2" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F2" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.07648514294522</v>
+        <v>2.937428835728598</v>
       </c>
       <c r="D3" t="n">
-        <v>18.5685180998581</v>
+        <v>3.017384191226941</v>
       </c>
       <c r="E3" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F3" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.89825912008808</v>
+        <v>3.883467107014314</v>
       </c>
       <c r="D4" t="n">
-        <v>24.098539364181</v>
+        <v>3.916012646679412</v>
       </c>
       <c r="E4" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F4" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.06413179569005</v>
+        <v>2.610421416799633</v>
       </c>
       <c r="D5" t="n">
-        <v>16.25710179238054</v>
+        <v>2.641779041261838</v>
       </c>
       <c r="E5" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F5" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.176551149535068</v>
+        <v>1.003689561799449</v>
       </c>
       <c r="D6" t="n">
-        <v>6.382191649785674</v>
+        <v>1.037106143090172</v>
       </c>
       <c r="E6" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F6" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.211289625459202</v>
+        <v>1.33433456413712</v>
       </c>
       <c r="D7" t="n">
-        <v>8.044703511433829</v>
+        <v>1.307264320607997</v>
       </c>
       <c r="E7" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F7" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.19453626230877</v>
+        <v>2.144112142625175</v>
       </c>
       <c r="D8" t="n">
-        <v>13.01405590166614</v>
+        <v>2.114784084020748</v>
       </c>
       <c r="E8" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F8" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.30855186131309</v>
+        <v>4.600139677463377</v>
       </c>
       <c r="D9" t="n">
-        <v>28.13012618726341</v>
+        <v>4.571145505430305</v>
       </c>
       <c r="E9" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F9" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.49721736374547</v>
+        <v>4.143297821608638</v>
       </c>
       <c r="D10" t="n">
-        <v>19.53566090310845</v>
+        <v>3.174544896755124</v>
       </c>
       <c r="E10" t="n">
-        <v>7.380918239311286</v>
+        <v>1.199399213888084</v>
       </c>
       <c r="F10" t="n">
-        <v>6.995573586842487</v>
+        <v>1.136780707861905</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
